--- a/smallScpu.xlsx
+++ b/smallScpu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\fpga\RemedyCpu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2807957F-BF38-49A5-BF6D-92272D5A5F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C5F72E-C3FF-47C3-8358-C45D70A54BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32595" yWindow="1215" windowWidth="21600" windowHeight="11385" xr2:uid="{3A39868E-190A-4BF2-AB5E-9F4B9A685441}"/>
+    <workbookView xWindow="7200" yWindow="1515" windowWidth="21600" windowHeight="11385" xr2:uid="{3A39868E-190A-4BF2-AB5E-9F4B9A685441}"/>
   </bookViews>
   <sheets>
     <sheet name="smallScpu" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>A</t>
   </si>
@@ -122,9 +122,6 @@
     <t>ioR</t>
   </si>
   <si>
-    <t>stPC</t>
-  </si>
-  <si>
     <t>Reti</t>
   </si>
   <si>
@@ -132,6 +129,12 @@
   </si>
   <si>
     <t>flash_req</t>
+  </si>
+  <si>
+    <t>Brk</t>
+  </si>
+  <si>
+    <t>Setpc</t>
   </si>
 </sst>
 </file>
@@ -851,7 +854,36 @@
     <cellStyle name="Vurgu5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Vurgu6" xfId="38" builtinId="49" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal style="medium">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1895,44 +1927,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{09D190A1-E981-42FD-9FD5-3F546185E411}" name="Tablo2" displayName="Tablo2" ref="A1:AG74" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
-  <autoFilter ref="A1:AG74" xr:uid="{09D190A1-E981-42FD-9FD5-3F546185E411}"/>
-  <tableColumns count="33">
-    <tableColumn id="1" xr3:uid="{E26736F7-E5B8-46ED-AC09-7917C861F5F9}" name="G" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{126FB57A-0881-4C60-809C-D4D8D930CC98}" name="F" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{7F2F754D-CF56-4C42-99DC-160CAB690D7A}" name="E" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{72E6E9C4-939B-4BBD-86CA-E806966A3709}" name="D" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{FA26EC11-1C21-4F84-B9C9-CE51B7B792CB}" name="C" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{12AF16F1-0ECB-43A7-96CA-C7C98009D4F9}" name="B" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{5813ACF0-9AA2-4DFB-9B8A-6CC80BE5A06B}" name="A" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{860020B2-8799-4DBA-8F0D-D2D6561ABF4E}" name="Sütun1" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{09D190A1-E981-42FD-9FD5-3F546185E411}" name="Tablo2" displayName="Tablo2" ref="A1:AH75" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A1:AH75" xr:uid="{09D190A1-E981-42FD-9FD5-3F546185E411}"/>
+  <tableColumns count="34">
+    <tableColumn id="1" xr3:uid="{E26736F7-E5B8-46ED-AC09-7917C861F5F9}" name="G" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{126FB57A-0881-4C60-809C-D4D8D930CC98}" name="F" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{7F2F754D-CF56-4C42-99DC-160CAB690D7A}" name="E" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{72E6E9C4-939B-4BBD-86CA-E806966A3709}" name="D" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{FA26EC11-1C21-4F84-B9C9-CE51B7B792CB}" name="C" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{12AF16F1-0ECB-43A7-96CA-C7C98009D4F9}" name="B" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{5813ACF0-9AA2-4DFB-9B8A-6CC80BE5A06B}" name="A" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{860020B2-8799-4DBA-8F0D-D2D6561ABF4E}" name="Sütun1" dataDxfId="27">
       <calculatedColumnFormula>_xlfn.TEXTJOIN("",TRUE,"0x0",UPPER(_xlfn.BASE(_xlfn.DECIMAL(_xlfn.TEXTJOIN("",TRUE,A2:G2),2),16)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{56A39127-82B7-472E-92C7-4B8AA299A80B}" name="muxb0" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{2695C163-DFB3-4EC6-A9AF-B3F30656F93F}" name="muxb1" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{1D0AA771-5252-4211-A97C-5DEC7B76B809}" name="muxb2" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{6A91E5A8-AA56-472E-BA07-02436CDB5D45}" name="aluop0" dataDxfId="22"/>
-    <tableColumn id="13" xr3:uid="{2C723CA1-8E63-4120-927D-5B955E2BB2A4}" name="aluop1" dataDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{61B09EAE-8FE5-42AC-822A-2785F325EA1B}" name="aluop2" dataDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{907DE936-757A-44F8-93BA-B6B3C9B33C48}" name="aluop3" dataDxfId="19"/>
-    <tableColumn id="16" xr3:uid="{B5567F9B-2B8F-4C8D-8F32-6F6673F53F5B}" name="aluop4" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{FE61BC84-4640-4E9B-8B60-B684A4F7CAED}" name="aluop5" dataDxfId="17"/>
-    <tableColumn id="18" xr3:uid="{BBC21992-4A18-4A42-A74C-0B42ECD7F36C}" name="WE" dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{68FF9185-EAC1-42FC-B1B5-BA0E33048F20}" name="sf" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{A61EE037-5991-4E07-965A-036BED37866A}" name="iem0" dataDxfId="14"/>
-    <tableColumn id="21" xr3:uid="{6DD0478B-EA0E-4568-8F03-9A32C428B44D}" name="iem1" dataDxfId="13"/>
-    <tableColumn id="22" xr3:uid="{F7F77D56-5979-434A-9075-19E81472DAB2}" name="br0" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{9ED459CB-C589-4427-8076-E795DDDB497F}" name="br1" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{39FA594D-68D2-4338-9E71-017598221EA5}" name="br2" dataDxfId="10"/>
-    <tableColumn id="25" xr3:uid="{4D46F658-CBBD-4ED6-BF45-2A6BB7722283}" name="muxA" dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{87007302-7B80-4489-B7E3-CA718BA64E5E}" name="ld" dataDxfId="8"/>
-    <tableColumn id="27" xr3:uid="{B3C05387-5527-49ED-A396-CAAF33C292E6}" name="st" dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{58DADA32-8FFA-455A-876D-B172671E6710}" name="abs" dataDxfId="6"/>
-    <tableColumn id="29" xr3:uid="{E408D9E0-95E9-4E52-8444-ACFBFCBD0B23}" name="ioW" dataDxfId="5"/>
-    <tableColumn id="30" xr3:uid="{414678D4-2F39-4DAC-881A-9FD56748FBC7}" name="ioR" dataDxfId="4"/>
-    <tableColumn id="31" xr3:uid="{9852F1E0-19F4-4958-B9F0-7EA156A1129E}" name="stPC" dataDxfId="3"/>
-    <tableColumn id="32" xr3:uid="{B5F75B48-A057-48EF-8213-55FF71126F15}" name="Reti" dataDxfId="2"/>
-    <tableColumn id="33" xr3:uid="{363DC000-16D2-40CD-8ABD-8AC6B6FADC47}" name="flash_req" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{56A39127-82B7-472E-92C7-4B8AA299A80B}" name="muxb0" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{2695C163-DFB3-4EC6-A9AF-B3F30656F93F}" name="muxb1" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{1D0AA771-5252-4211-A97C-5DEC7B76B809}" name="muxb2" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{6A91E5A8-AA56-472E-BA07-02436CDB5D45}" name="aluop0" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{2C723CA1-8E63-4120-927D-5B955E2BB2A4}" name="aluop1" dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{61B09EAE-8FE5-42AC-822A-2785F325EA1B}" name="aluop2" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{907DE936-757A-44F8-93BA-B6B3C9B33C48}" name="aluop3" dataDxfId="20"/>
+    <tableColumn id="16" xr3:uid="{B5567F9B-2B8F-4C8D-8F32-6F6673F53F5B}" name="aluop4" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{FE61BC84-4640-4E9B-8B60-B684A4F7CAED}" name="aluop5" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{BBC21992-4A18-4A42-A74C-0B42ECD7F36C}" name="WE" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{68FF9185-EAC1-42FC-B1B5-BA0E33048F20}" name="sf" dataDxfId="16"/>
+    <tableColumn id="20" xr3:uid="{A61EE037-5991-4E07-965A-036BED37866A}" name="iem0" dataDxfId="15"/>
+    <tableColumn id="21" xr3:uid="{6DD0478B-EA0E-4568-8F03-9A32C428B44D}" name="iem1" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{F7F77D56-5979-434A-9075-19E81472DAB2}" name="br0" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{9ED459CB-C589-4427-8076-E795DDDB497F}" name="br1" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{39FA594D-68D2-4338-9E71-017598221EA5}" name="br2" dataDxfId="11"/>
+    <tableColumn id="25" xr3:uid="{4D46F658-CBBD-4ED6-BF45-2A6BB7722283}" name="muxA" dataDxfId="10"/>
+    <tableColumn id="26" xr3:uid="{87007302-7B80-4489-B7E3-CA718BA64E5E}" name="ld" dataDxfId="9"/>
+    <tableColumn id="27" xr3:uid="{B3C05387-5527-49ED-A396-CAAF33C292E6}" name="st" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{58DADA32-8FFA-455A-876D-B172671E6710}" name="abs" dataDxfId="7"/>
+    <tableColumn id="29" xr3:uid="{E408D9E0-95E9-4E52-8444-ACFBFCBD0B23}" name="ioW" dataDxfId="6"/>
+    <tableColumn id="30" xr3:uid="{414678D4-2F39-4DAC-881A-9FD56748FBC7}" name="ioR" dataDxfId="5"/>
+    <tableColumn id="31" xr3:uid="{9852F1E0-19F4-4958-B9F0-7EA156A1129E}" name="Setpc" dataDxfId="4"/>
+    <tableColumn id="32" xr3:uid="{B5F75B48-A057-48EF-8213-55FF71126F15}" name="Reti" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{363DC000-16D2-40CD-8ABD-8AC6B6FADC47}" name="flash_req" dataDxfId="2"/>
+    <tableColumn id="34" xr3:uid="{A99D3146-4BAF-4852-A6BF-F64F86604259}" name="Brk" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2255,7 +2288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81354689-963F-4965-A0AF-6C68040592CE}">
-  <dimension ref="A1:AG74"/>
+  <dimension ref="A1:AT75"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="14"/>
@@ -2275,9 +2308,10 @@
     <col min="31" max="31" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="25" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:34" s="25" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
         <v>6</v>
       </c>
@@ -2300,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I1" s="24" t="s">
         <v>7</v>
@@ -2369,16 +2403,19 @@
         <v>28</v>
       </c>
       <c r="AE1" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF1" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="25" t="s">
-        <v>30</v>
-      </c>
       <c r="AG1" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="25" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -2479,8 +2516,11 @@
       <c r="AG2" s="7">
         <v>0</v>
       </c>
+      <c r="AH2" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -2581,8 +2621,11 @@
       <c r="AG3" s="7">
         <v>0</v>
       </c>
+      <c r="AH3" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>0</v>
       </c>
@@ -2683,8 +2726,11 @@
       <c r="AG4" s="7">
         <v>0</v>
       </c>
+      <c r="AH4" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -2785,8 +2831,11 @@
       <c r="AG5" s="7">
         <v>0</v>
       </c>
+      <c r="AH5" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>0</v>
       </c>
@@ -2887,8 +2936,11 @@
       <c r="AG6" s="7">
         <v>0</v>
       </c>
+      <c r="AH6" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>0</v>
       </c>
@@ -2989,8 +3041,11 @@
       <c r="AG7" s="7">
         <v>0</v>
       </c>
+      <c r="AH7" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>0</v>
       </c>
@@ -3091,8 +3146,11 @@
       <c r="AG8" s="7">
         <v>0</v>
       </c>
+      <c r="AH8" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>0</v>
       </c>
@@ -3193,8 +3251,11 @@
       <c r="AG9" s="7">
         <v>0</v>
       </c>
+      <c r="AH9" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>0</v>
       </c>
@@ -3295,8 +3356,11 @@
       <c r="AG10" s="7">
         <v>0</v>
       </c>
+      <c r="AH10" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>0</v>
       </c>
@@ -3397,8 +3461,11 @@
       <c r="AG11" s="7">
         <v>0</v>
       </c>
+      <c r="AH11" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>0</v>
       </c>
@@ -3499,8 +3566,11 @@
       <c r="AG12" s="7">
         <v>0</v>
       </c>
+      <c r="AH12" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>0</v>
       </c>
@@ -3601,8 +3671,11 @@
       <c r="AG13" s="7">
         <v>0</v>
       </c>
+      <c r="AH13" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>0</v>
       </c>
@@ -3703,8 +3776,11 @@
       <c r="AG14" s="7">
         <v>0</v>
       </c>
+      <c r="AH14" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>0</v>
       </c>
@@ -3805,8 +3881,11 @@
       <c r="AG15" s="7">
         <v>0</v>
       </c>
+      <c r="AH15" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>0</v>
       </c>
@@ -3907,8 +3986,11 @@
       <c r="AG16" s="7">
         <v>0</v>
       </c>
+      <c r="AH16" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>0</v>
       </c>
@@ -4009,8 +4091,11 @@
       <c r="AG17" s="7">
         <v>0</v>
       </c>
+      <c r="AH17" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>0</v>
       </c>
@@ -4111,8 +4196,11 @@
       <c r="AG18" s="7">
         <v>0</v>
       </c>
+      <c r="AH18" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>0</v>
       </c>
@@ -4213,8 +4301,11 @@
       <c r="AG19" s="7">
         <v>0</v>
       </c>
+      <c r="AH19" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>0</v>
       </c>
@@ -4315,8 +4406,11 @@
       <c r="AG20" s="7">
         <v>0</v>
       </c>
+      <c r="AH20" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>0</v>
       </c>
@@ -4417,8 +4511,11 @@
       <c r="AG21" s="7">
         <v>0</v>
       </c>
+      <c r="AH21" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>0</v>
       </c>
@@ -4519,8 +4616,11 @@
       <c r="AG22" s="7">
         <v>0</v>
       </c>
+      <c r="AH22" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>0</v>
       </c>
@@ -4621,8 +4721,11 @@
       <c r="AG23" s="7">
         <v>0</v>
       </c>
+      <c r="AH23" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>0</v>
       </c>
@@ -4723,8 +4826,11 @@
       <c r="AG24" s="7">
         <v>0</v>
       </c>
+      <c r="AH24" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>0</v>
       </c>
@@ -4825,8 +4931,11 @@
       <c r="AG25" s="7">
         <v>0</v>
       </c>
+      <c r="AH25" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>0</v>
       </c>
@@ -4927,8 +5036,11 @@
       <c r="AG26" s="7">
         <v>0</v>
       </c>
+      <c r="AH26" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>0</v>
       </c>
@@ -5029,8 +5141,11 @@
       <c r="AG27" s="7">
         <v>0</v>
       </c>
+      <c r="AH27" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>0</v>
       </c>
@@ -5131,8 +5246,11 @@
       <c r="AG28" s="7">
         <v>0</v>
       </c>
+      <c r="AH28" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:33" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:34" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="15">
         <v>0</v>
       </c>
@@ -5233,8 +5351,11 @@
       <c r="AG29" s="7">
         <v>0</v>
       </c>
+      <c r="AH29" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:33" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:34" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="15">
         <v>0</v>
       </c>
@@ -5335,8 +5456,11 @@
       <c r="AG30" s="7">
         <v>0</v>
       </c>
+      <c r="AH30" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:33" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:34" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="15">
         <v>0</v>
       </c>
@@ -5437,8 +5561,11 @@
       <c r="AG31" s="7">
         <v>0</v>
       </c>
+      <c r="AH31" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>0</v>
       </c>
@@ -5539,8 +5666,11 @@
       <c r="AG32" s="7">
         <v>0</v>
       </c>
+      <c r="AH32" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>0</v>
       </c>
@@ -5641,8 +5771,11 @@
       <c r="AG33" s="7">
         <v>0</v>
       </c>
+      <c r="AH33" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>0</v>
       </c>
@@ -5743,8 +5876,11 @@
       <c r="AG34" s="7">
         <v>0</v>
       </c>
+      <c r="AH34" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>0</v>
       </c>
@@ -5845,8 +5981,11 @@
       <c r="AG35" s="7">
         <v>0</v>
       </c>
+      <c r="AH35" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>0</v>
       </c>
@@ -5947,8 +6086,11 @@
       <c r="AG36" s="7">
         <v>0</v>
       </c>
+      <c r="AH36" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>0</v>
       </c>
@@ -6049,8 +6191,11 @@
       <c r="AG37" s="7">
         <v>0</v>
       </c>
+      <c r="AH37" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>0</v>
       </c>
@@ -6151,8 +6296,11 @@
       <c r="AG38" s="7">
         <v>0</v>
       </c>
+      <c r="AH38" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="39" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>0</v>
       </c>
@@ -6253,8 +6401,11 @@
       <c r="AG39" s="7">
         <v>0</v>
       </c>
+      <c r="AH39" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>0</v>
       </c>
@@ -6355,8 +6506,11 @@
       <c r="AG40" s="7">
         <v>0</v>
       </c>
+      <c r="AH40" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>0</v>
       </c>
@@ -6457,8 +6611,11 @@
       <c r="AG41" s="7">
         <v>0</v>
       </c>
+      <c r="AH41" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>0</v>
       </c>
@@ -6559,8 +6716,11 @@
       <c r="AG42" s="7">
         <v>0</v>
       </c>
+      <c r="AH42" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>0</v>
       </c>
@@ -6661,8 +6821,11 @@
       <c r="AG43" s="7">
         <v>0</v>
       </c>
+      <c r="AH43" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>0</v>
       </c>
@@ -6763,8 +6926,11 @@
       <c r="AG44" s="7">
         <v>0</v>
       </c>
+      <c r="AH44" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>0</v>
       </c>
@@ -6865,8 +7031,11 @@
       <c r="AG45" s="7">
         <v>0</v>
       </c>
+      <c r="AH45" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>0</v>
       </c>
@@ -6967,8 +7136,11 @@
       <c r="AG46" s="7">
         <v>0</v>
       </c>
+      <c r="AH46" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>0</v>
       </c>
@@ -7069,8 +7241,11 @@
       <c r="AG47" s="7">
         <v>0</v>
       </c>
+      <c r="AH47" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>0</v>
       </c>
@@ -7171,8 +7346,11 @@
       <c r="AG48" s="7">
         <v>0</v>
       </c>
+      <c r="AH48" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>0</v>
       </c>
@@ -7273,8 +7451,11 @@
       <c r="AG49" s="7">
         <v>0</v>
       </c>
+      <c r="AH49" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>0</v>
       </c>
@@ -7375,8 +7556,11 @@
       <c r="AG50" s="7">
         <v>0</v>
       </c>
+      <c r="AH50" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>0</v>
       </c>
@@ -7477,8 +7661,11 @@
       <c r="AG51" s="7">
         <v>0</v>
       </c>
+      <c r="AH51" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>0</v>
       </c>
@@ -7579,8 +7766,11 @@
       <c r="AG52" s="7">
         <v>0</v>
       </c>
+      <c r="AH52" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:33" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:34" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="15">
         <v>0</v>
       </c>
@@ -7681,8 +7871,11 @@
       <c r="AG53" s="7">
         <v>0</v>
       </c>
+      <c r="AH53" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>0</v>
       </c>
@@ -7708,8 +7901,8 @@
         <f t="shared" si="1"/>
         <v>0x34</v>
       </c>
-      <c r="I54" s="8">
-        <v>1</v>
+      <c r="I54" s="18">
+        <v>0</v>
       </c>
       <c r="J54" s="7">
         <v>1</v>
@@ -7742,7 +7935,7 @@
         <v>0</v>
       </c>
       <c r="T54" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" s="7">
         <v>0</v>
@@ -7783,8 +7976,11 @@
       <c r="AG54" s="7">
         <v>0</v>
       </c>
+      <c r="AH54" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>0</v>
       </c>
@@ -7810,8 +8006,8 @@
         <f t="shared" si="1"/>
         <v>0x35</v>
       </c>
-      <c r="I55" s="8">
-        <v>1</v>
+      <c r="I55" s="18">
+        <v>0</v>
       </c>
       <c r="J55" s="7">
         <v>1</v>
@@ -7844,7 +8040,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U55" s="7">
         <v>0</v>
@@ -7885,8 +8081,11 @@
       <c r="AG55" s="7">
         <v>0</v>
       </c>
+      <c r="AH55" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>0</v>
       </c>
@@ -7912,8 +8111,8 @@
         <f t="shared" si="1"/>
         <v>0x36</v>
       </c>
-      <c r="I56" s="8">
-        <v>1</v>
+      <c r="I56" s="18">
+        <v>0</v>
       </c>
       <c r="J56" s="7">
         <v>1</v>
@@ -7946,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U56" s="7">
         <v>0</v>
@@ -7987,8 +8186,11 @@
       <c r="AG56" s="7">
         <v>0</v>
       </c>
+      <c r="AH56" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>0</v>
       </c>
@@ -8014,8 +8216,8 @@
         <f t="shared" si="1"/>
         <v>0x37</v>
       </c>
-      <c r="I57" s="8">
-        <v>1</v>
+      <c r="I57" s="18">
+        <v>0</v>
       </c>
       <c r="J57" s="7">
         <v>1</v>
@@ -8048,7 +8250,7 @@
         <v>0</v>
       </c>
       <c r="T57" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U57" s="7">
         <v>0</v>
@@ -8089,8 +8291,11 @@
       <c r="AG57" s="7">
         <v>0</v>
       </c>
+      <c r="AH57" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>0</v>
       </c>
@@ -8116,8 +8321,8 @@
         <f t="shared" si="1"/>
         <v>0x38</v>
       </c>
-      <c r="I58" s="8">
-        <v>1</v>
+      <c r="I58" s="18">
+        <v>0</v>
       </c>
       <c r="J58" s="7">
         <v>1</v>
@@ -8150,7 +8355,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U58" s="7">
         <v>0</v>
@@ -8191,8 +8396,11 @@
       <c r="AG58" s="7">
         <v>0</v>
       </c>
+      <c r="AH58" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>0</v>
       </c>
@@ -8218,8 +8426,8 @@
         <f t="shared" si="1"/>
         <v>0x39</v>
       </c>
-      <c r="I59" s="8">
-        <v>1</v>
+      <c r="I59" s="18">
+        <v>0</v>
       </c>
       <c r="J59" s="7">
         <v>1</v>
@@ -8252,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="T59" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U59" s="7">
         <v>0</v>
@@ -8293,8 +8501,11 @@
       <c r="AG59" s="7">
         <v>0</v>
       </c>
+      <c r="AH59" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>0</v>
       </c>
@@ -8395,8 +8606,11 @@
       <c r="AG60" s="7">
         <v>0</v>
       </c>
+      <c r="AH60" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>0</v>
       </c>
@@ -8497,8 +8711,11 @@
       <c r="AG61" s="7">
         <v>0</v>
       </c>
+      <c r="AH61" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>0</v>
       </c>
@@ -8599,8 +8816,11 @@
       <c r="AG62" s="7">
         <v>0</v>
       </c>
+      <c r="AH62" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>0</v>
       </c>
@@ -8701,8 +8921,11 @@
       <c r="AG63" s="7">
         <v>0</v>
       </c>
+      <c r="AH63" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>0</v>
       </c>
@@ -8803,8 +9026,11 @@
       <c r="AG64" s="7">
         <v>0</v>
       </c>
+      <c r="AH64" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>0</v>
       </c>
@@ -8905,8 +9131,11 @@
       <c r="AG65" s="7">
         <v>0</v>
       </c>
+      <c r="AH65" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>1</v>
       </c>
@@ -9007,8 +9236,11 @@
       <c r="AG66" s="7">
         <v>0</v>
       </c>
+      <c r="AH66" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="67" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>1</v>
       </c>
@@ -9109,8 +9341,11 @@
       <c r="AG67" s="7">
         <v>0</v>
       </c>
+      <c r="AH67" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="68" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>1</v>
       </c>
@@ -9211,8 +9446,11 @@
       <c r="AG68" s="7">
         <v>0</v>
       </c>
+      <c r="AH68" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>1</v>
       </c>
@@ -9313,8 +9551,11 @@
       <c r="AG69" s="7">
         <v>0</v>
       </c>
+      <c r="AH69" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="9">
         <v>1</v>
       </c>
@@ -9415,8 +9656,11 @@
       <c r="AG70" s="7">
         <v>0</v>
       </c>
+      <c r="AH70" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="1:33" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9">
         <v>1</v>
       </c>
@@ -9517,8 +9761,23 @@
       <c r="AG71" s="7">
         <v>1</v>
       </c>
+      <c r="AH71" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="5"/>
+      <c r="AJ71" s="5"/>
+      <c r="AK71" s="5"/>
+      <c r="AL71" s="5"/>
+      <c r="AM71" s="5"/>
+      <c r="AN71" s="5"/>
+      <c r="AO71" s="5"/>
+      <c r="AP71" s="5"/>
+      <c r="AQ71" s="5"/>
+      <c r="AR71" s="5"/>
+      <c r="AS71" s="5"/>
+      <c r="AT71" s="5"/>
     </row>
-    <row r="72" spans="1:33" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9">
         <v>1</v>
       </c>
@@ -9619,8 +9878,23 @@
       <c r="AG72" s="7">
         <v>1</v>
       </c>
+      <c r="AH72" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="5"/>
+      <c r="AJ72" s="5"/>
+      <c r="AK72" s="5"/>
+      <c r="AL72" s="5"/>
+      <c r="AM72" s="5"/>
+      <c r="AN72" s="5"/>
+      <c r="AO72" s="5"/>
+      <c r="AP72" s="5"/>
+      <c r="AQ72" s="5"/>
+      <c r="AR72" s="5"/>
+      <c r="AS72" s="5"/>
+      <c r="AT72" s="5"/>
     </row>
-    <row r="73" spans="1:33" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9">
         <v>1</v>
       </c>
@@ -9721,8 +9995,23 @@
       <c r="AG73" s="7">
         <v>1</v>
       </c>
+      <c r="AH73" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="5"/>
+      <c r="AJ73" s="5"/>
+      <c r="AK73" s="5"/>
+      <c r="AL73" s="5"/>
+      <c r="AM73" s="5"/>
+      <c r="AN73" s="5"/>
+      <c r="AO73" s="5"/>
+      <c r="AP73" s="5"/>
+      <c r="AQ73" s="5"/>
+      <c r="AR73" s="5"/>
+      <c r="AS73" s="5"/>
+      <c r="AT73" s="5"/>
     </row>
-    <row r="74" spans="1:33" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
         <v>1</v>
       </c>
@@ -9823,13 +10112,145 @@
       <c r="AG74" s="7">
         <v>1</v>
       </c>
+      <c r="AH74" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="5"/>
+      <c r="AJ74" s="5"/>
+      <c r="AK74" s="5"/>
+      <c r="AL74" s="5"/>
+      <c r="AM74" s="5"/>
+      <c r="AN74" s="5"/>
+      <c r="AO74" s="5"/>
+      <c r="AP74" s="5"/>
+      <c r="AQ74" s="5"/>
+      <c r="AR74" s="5"/>
+      <c r="AS74" s="5"/>
+      <c r="AT74" s="5"/>
+    </row>
+    <row r="75" spans="1:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="9">
+        <v>1</v>
+      </c>
+      <c r="B75" s="10">
+        <v>0</v>
+      </c>
+      <c r="C75" s="10">
+        <v>0</v>
+      </c>
+      <c r="D75" s="11">
+        <v>1</v>
+      </c>
+      <c r="E75" s="11">
+        <v>0</v>
+      </c>
+      <c r="F75" s="11">
+        <v>0</v>
+      </c>
+      <c r="G75" s="11">
+        <v>1</v>
+      </c>
+      <c r="H75" s="12" t="str">
+        <f>_xlfn.TEXTJOIN("",TRUE,"0x0",UPPER(_xlfn.BASE(_xlfn.DECIMAL(_xlfn.TEXTJOIN("",TRUE,A75:G75),2),16)))</f>
+        <v>0x049</v>
+      </c>
+      <c r="I75" s="27">
+        <v>0</v>
+      </c>
+      <c r="J75" s="26">
+        <v>0</v>
+      </c>
+      <c r="K75" s="26">
+        <v>0</v>
+      </c>
+      <c r="L75" s="26">
+        <v>0</v>
+      </c>
+      <c r="M75" s="26">
+        <v>0</v>
+      </c>
+      <c r="N75" s="26">
+        <v>0</v>
+      </c>
+      <c r="O75" s="26">
+        <v>0</v>
+      </c>
+      <c r="P75" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="26">
+        <v>0</v>
+      </c>
+      <c r="R75" s="26">
+        <v>0</v>
+      </c>
+      <c r="S75" s="26">
+        <v>0</v>
+      </c>
+      <c r="T75" s="26">
+        <v>0</v>
+      </c>
+      <c r="U75" s="26">
+        <v>0</v>
+      </c>
+      <c r="V75" s="26">
+        <v>0</v>
+      </c>
+      <c r="W75" s="26">
+        <v>0</v>
+      </c>
+      <c r="X75" s="26">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="26">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="26">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="26">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="26">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="26">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="26">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="26">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="26">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="26">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="26">
+        <v>1</v>
+      </c>
+      <c r="AI75" s="5"/>
+      <c r="AJ75" s="5"/>
+      <c r="AK75" s="5"/>
+      <c r="AL75" s="5"/>
+      <c r="AM75" s="5"/>
+      <c r="AN75" s="5"/>
+      <c r="AO75" s="5"/>
+      <c r="AP75" s="5"/>
+      <c r="AQ75" s="5"/>
+      <c r="AR75" s="5"/>
+      <c r="AS75" s="5"/>
+      <c r="AT75" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="H34:H35">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:AG74">
+  <conditionalFormatting sqref="H2:AH75">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -9841,8 +10262,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I72:AG72 I73:AF73 AG73:AG74">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="I74:AF75 AG75:AH75">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9853,8 +10274,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I74:AF74">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="I72:AG72 I73:AF73 AG73:AG75 AH75">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/smallScpu.xlsx
+++ b/smallScpu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\fpga\RemedyCpu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C5F72E-C3FF-47C3-8358-C45D70A54BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1886A4-C869-4F29-88C4-A01ADEF2E51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="1515" windowWidth="21600" windowHeight="11385" xr2:uid="{3A39868E-190A-4BF2-AB5E-9F4B9A685441}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3A39868E-190A-4BF2-AB5E-9F4B9A685441}"/>
   </bookViews>
   <sheets>
     <sheet name="smallScpu" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>A</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>aluop4</t>
-  </si>
-  <si>
-    <t>aluop5</t>
   </si>
   <si>
     <t>WE</t>
@@ -854,36 +851,7 @@
     <cellStyle name="Vurgu5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Vurgu6" xfId="38" builtinId="49" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="37">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal style="medium">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
+  <dxfs count="36">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1927,28 +1895,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{09D190A1-E981-42FD-9FD5-3F546185E411}" name="Tablo2" displayName="Tablo2" ref="A1:AH75" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="A1:AH75" xr:uid="{09D190A1-E981-42FD-9FD5-3F546185E411}"/>
-  <tableColumns count="34">
-    <tableColumn id="1" xr3:uid="{E26736F7-E5B8-46ED-AC09-7917C861F5F9}" name="G" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{126FB57A-0881-4C60-809C-D4D8D930CC98}" name="F" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{7F2F754D-CF56-4C42-99DC-160CAB690D7A}" name="E" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{72E6E9C4-939B-4BBD-86CA-E806966A3709}" name="D" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{FA26EC11-1C21-4F84-B9C9-CE51B7B792CB}" name="C" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{12AF16F1-0ECB-43A7-96CA-C7C98009D4F9}" name="B" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{5813ACF0-9AA2-4DFB-9B8A-6CC80BE5A06B}" name="A" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{860020B2-8799-4DBA-8F0D-D2D6561ABF4E}" name="Sütun1" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{09D190A1-E981-42FD-9FD5-3F546185E411}" name="Tablo2" displayName="Tablo2" ref="A1:AG75" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
+  <autoFilter ref="A1:AG75" xr:uid="{09D190A1-E981-42FD-9FD5-3F546185E411}"/>
+  <tableColumns count="33">
+    <tableColumn id="1" xr3:uid="{E26736F7-E5B8-46ED-AC09-7917C861F5F9}" name="G" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{126FB57A-0881-4C60-809C-D4D8D930CC98}" name="F" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{7F2F754D-CF56-4C42-99DC-160CAB690D7A}" name="E" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{72E6E9C4-939B-4BBD-86CA-E806966A3709}" name="D" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{FA26EC11-1C21-4F84-B9C9-CE51B7B792CB}" name="C" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{12AF16F1-0ECB-43A7-96CA-C7C98009D4F9}" name="B" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{5813ACF0-9AA2-4DFB-9B8A-6CC80BE5A06B}" name="A" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{860020B2-8799-4DBA-8F0D-D2D6561ABF4E}" name="Sütun1" dataDxfId="26">
       <calculatedColumnFormula>_xlfn.TEXTJOIN("",TRUE,"0x0",UPPER(_xlfn.BASE(_xlfn.DECIMAL(_xlfn.TEXTJOIN("",TRUE,A2:G2),2),16)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{56A39127-82B7-472E-92C7-4B8AA299A80B}" name="muxb0" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{2695C163-DFB3-4EC6-A9AF-B3F30656F93F}" name="muxb1" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{1D0AA771-5252-4211-A97C-5DEC7B76B809}" name="muxb2" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{6A91E5A8-AA56-472E-BA07-02436CDB5D45}" name="aluop0" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{2C723CA1-8E63-4120-927D-5B955E2BB2A4}" name="aluop1" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{61B09EAE-8FE5-42AC-822A-2785F325EA1B}" name="aluop2" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{907DE936-757A-44F8-93BA-B6B3C9B33C48}" name="aluop3" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{B5567F9B-2B8F-4C8D-8F32-6F6673F53F5B}" name="aluop4" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{FE61BC84-4640-4E9B-8B60-B684A4F7CAED}" name="aluop5" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{56A39127-82B7-472E-92C7-4B8AA299A80B}" name="muxb0" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{2695C163-DFB3-4EC6-A9AF-B3F30656F93F}" name="muxb1" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{1D0AA771-5252-4211-A97C-5DEC7B76B809}" name="muxb2" dataDxfId="23"/>
+    <tableColumn id="12" xr3:uid="{6A91E5A8-AA56-472E-BA07-02436CDB5D45}" name="aluop0" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{2C723CA1-8E63-4120-927D-5B955E2BB2A4}" name="aluop1" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{61B09EAE-8FE5-42AC-822A-2785F325EA1B}" name="aluop2" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{907DE936-757A-44F8-93BA-B6B3C9B33C48}" name="aluop3" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{FE61BC84-4640-4E9B-8B60-B684A4F7CAED}" name="aluop4" dataDxfId="18"/>
     <tableColumn id="18" xr3:uid="{BBC21992-4A18-4A42-A74C-0B42ECD7F36C}" name="WE" dataDxfId="17"/>
     <tableColumn id="19" xr3:uid="{68FF9185-EAC1-42FC-B1B5-BA0E33048F20}" name="sf" dataDxfId="16"/>
     <tableColumn id="20" xr3:uid="{A61EE037-5991-4E07-965A-036BED37866A}" name="iem0" dataDxfId="15"/>
@@ -1965,7 +1932,7 @@
     <tableColumn id="31" xr3:uid="{9852F1E0-19F4-4958-B9F0-7EA156A1129E}" name="Setpc" dataDxfId="4"/>
     <tableColumn id="32" xr3:uid="{B5F75B48-A057-48EF-8213-55FF71126F15}" name="Reti" dataDxfId="3"/>
     <tableColumn id="33" xr3:uid="{363DC000-16D2-40CD-8ABD-8AC6B6FADC47}" name="flash_req" dataDxfId="2"/>
-    <tableColumn id="34" xr3:uid="{A99D3146-4BAF-4852-A6BF-F64F86604259}" name="Brk" dataDxfId="0"/>
+    <tableColumn id="34" xr3:uid="{A99D3146-4BAF-4852-A6BF-F64F86604259}" name="Brk" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2288,30 +2255,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81354689-963F-4965-A0AF-6C68040592CE}">
-  <dimension ref="A1:AT75"/>
+  <dimension ref="A1:AS75"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="14"/>
     <col min="8" max="8" width="9.140625" style="13"/>
     <col min="9" max="12" width="13.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.140625" style="1" customWidth="1"/>
-    <col min="14" max="17" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="9.140625" style="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.140625" style="1"/>
-    <col min="29" max="29" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="25" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:33" s="25" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20" t="s">
         <v>6</v>
       </c>
@@ -2334,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I1" s="24" t="s">
         <v>7</v>
@@ -2400,22 +2368,19 @@
         <v>27</v>
       </c>
       <c r="AD1" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE1" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="25" t="s">
-        <v>33</v>
-      </c>
       <c r="AF1" s="25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG1" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="25" t="s">
-        <v>32</v>
-      </c>
     </row>
-    <row r="2" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -2516,11 +2481,8 @@
       <c r="AG2" s="7">
         <v>0</v>
       </c>
-      <c r="AH2" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -2571,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="Q3" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="7">
         <v>0</v>
@@ -2621,11 +2583,8 @@
       <c r="AG3" s="7">
         <v>0</v>
       </c>
-      <c r="AH3" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>0</v>
       </c>
@@ -2673,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="7">
         <v>1</v>
@@ -2682,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="S4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" s="7">
         <v>0</v>
@@ -2726,11 +2685,8 @@
       <c r="AG4" s="7">
         <v>0</v>
       </c>
-      <c r="AH4" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -2778,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="7">
         <v>1</v>
@@ -2787,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="S5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" s="7">
         <v>0</v>
@@ -2831,11 +2787,8 @@
       <c r="AG5" s="7">
         <v>0</v>
       </c>
-      <c r="AH5" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>0</v>
       </c>
@@ -2886,13 +2839,13 @@
         <v>0</v>
       </c>
       <c r="Q6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="7">
         <v>1</v>
       </c>
       <c r="S6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" s="7">
         <v>0</v>
@@ -2936,11 +2889,8 @@
       <c r="AG6" s="7">
         <v>0</v>
       </c>
-      <c r="AH6" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>0</v>
       </c>
@@ -2991,13 +2941,13 @@
         <v>0</v>
       </c>
       <c r="Q7" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="7">
         <v>1</v>
       </c>
       <c r="S7" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" s="7">
         <v>0</v>
@@ -3041,11 +2991,8 @@
       <c r="AG7" s="7">
         <v>0</v>
       </c>
-      <c r="AH7" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>0</v>
       </c>
@@ -3093,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="P8" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="7">
         <v>1</v>
@@ -3102,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="S8" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" s="7">
         <v>0</v>
@@ -3146,11 +3093,8 @@
       <c r="AG8" s="7">
         <v>0</v>
       </c>
-      <c r="AH8" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>0</v>
       </c>
@@ -3201,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="Q9" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="7">
         <v>1</v>
       </c>
       <c r="S9" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" s="7">
         <v>0</v>
@@ -3251,11 +3195,8 @@
       <c r="AG9" s="7">
         <v>0</v>
       </c>
-      <c r="AH9" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>0</v>
       </c>
@@ -3303,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="7">
         <v>1</v>
@@ -3312,7 +3253,7 @@
         <v>1</v>
       </c>
       <c r="S10" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" s="7">
         <v>0</v>
@@ -3356,11 +3297,8 @@
       <c r="AG10" s="7">
         <v>0</v>
       </c>
-      <c r="AH10" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>0</v>
       </c>
@@ -3411,16 +3349,16 @@
         <v>0</v>
       </c>
       <c r="Q11" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" s="7">
         <v>0</v>
@@ -3461,11 +3399,8 @@
       <c r="AG11" s="7">
         <v>0</v>
       </c>
-      <c r="AH11" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>0</v>
       </c>
@@ -3516,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="Q12" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="7">
         <v>0</v>
@@ -3566,11 +3501,8 @@
       <c r="AG12" s="7">
         <v>0</v>
       </c>
-      <c r="AH12" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>0</v>
       </c>
@@ -3618,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="7">
         <v>1</v>
@@ -3630,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" s="7">
         <v>0</v>
@@ -3671,11 +3603,8 @@
       <c r="AG13" s="7">
         <v>0</v>
       </c>
-      <c r="AH13" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>0</v>
       </c>
@@ -3723,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="7">
         <v>1</v>
@@ -3732,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="S14" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" s="7">
         <v>0</v>
@@ -3776,11 +3705,8 @@
       <c r="AG14" s="7">
         <v>0</v>
       </c>
-      <c r="AH14" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="15" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>0</v>
       </c>
@@ -3828,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="7">
         <v>1</v>
@@ -3840,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15" s="7">
         <v>0</v>
@@ -3881,11 +3807,8 @@
       <c r="AG15" s="7">
         <v>0</v>
       </c>
-      <c r="AH15" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="16" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>0</v>
       </c>
@@ -3933,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="7">
         <v>1</v>
@@ -3942,7 +3865,7 @@
         <v>1</v>
       </c>
       <c r="S16" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" s="7">
         <v>0</v>
@@ -3986,11 +3909,8 @@
       <c r="AG16" s="7">
         <v>0</v>
       </c>
-      <c r="AH16" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="17" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>0</v>
       </c>
@@ -4041,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="7">
         <v>1</v>
@@ -4050,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="T17" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" s="7">
         <v>0</v>
@@ -4091,11 +4011,8 @@
       <c r="AG17" s="7">
         <v>0</v>
       </c>
-      <c r="AH17" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="18" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>0</v>
       </c>
@@ -4146,13 +4063,13 @@
         <v>0</v>
       </c>
       <c r="Q18" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="7">
         <v>1</v>
       </c>
       <c r="S18" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" s="7">
         <v>0</v>
@@ -4196,11 +4113,8 @@
       <c r="AG18" s="7">
         <v>0</v>
       </c>
-      <c r="AH18" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="19" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>0</v>
       </c>
@@ -4251,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="7">
         <v>1</v>
@@ -4260,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="T19" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19" s="7">
         <v>0</v>
@@ -4301,11 +4215,8 @@
       <c r="AG19" s="7">
         <v>0</v>
       </c>
-      <c r="AH19" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="20" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>0</v>
       </c>
@@ -4356,13 +4267,13 @@
         <v>0</v>
       </c>
       <c r="Q20" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="7">
         <v>1</v>
       </c>
       <c r="S20" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" s="7">
         <v>0</v>
@@ -4406,11 +4317,8 @@
       <c r="AG20" s="7">
         <v>0</v>
       </c>
-      <c r="AH20" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="21" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>0</v>
       </c>
@@ -4458,13 +4366,13 @@
         <v>1</v>
       </c>
       <c r="P21" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="7">
         <v>1</v>
       </c>
       <c r="R21" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" s="7">
         <v>0</v>
@@ -4511,11 +4419,8 @@
       <c r="AG21" s="7">
         <v>0</v>
       </c>
-      <c r="AH21" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="22" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>0</v>
       </c>
@@ -4563,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="P22" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="7">
         <v>1</v>
@@ -4575,7 +4480,7 @@
         <v>1</v>
       </c>
       <c r="T22" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" s="7">
         <v>0</v>
@@ -4616,11 +4521,8 @@
       <c r="AG22" s="7">
         <v>0</v>
       </c>
-      <c r="AH22" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="23" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>0</v>
       </c>
@@ -4668,7 +4570,7 @@
         <v>1</v>
       </c>
       <c r="P23" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="7">
         <v>1</v>
@@ -4677,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="S23" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" s="7">
         <v>0</v>
@@ -4721,11 +4623,8 @@
       <c r="AG23" s="7">
         <v>0</v>
       </c>
-      <c r="AH23" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="24" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>0</v>
       </c>
@@ -4776,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="7">
         <v>1</v>
@@ -4785,7 +4684,7 @@
         <v>1</v>
       </c>
       <c r="T24" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" s="7">
         <v>0</v>
@@ -4826,11 +4725,8 @@
       <c r="AG24" s="7">
         <v>0</v>
       </c>
-      <c r="AH24" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="25" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>0</v>
       </c>
@@ -4881,13 +4777,13 @@
         <v>0</v>
       </c>
       <c r="Q25" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="7">
         <v>1</v>
       </c>
       <c r="S25" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" s="7">
         <v>0</v>
@@ -4931,11 +4827,8 @@
       <c r="AG25" s="7">
         <v>0</v>
       </c>
-      <c r="AH25" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="26" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>0</v>
       </c>
@@ -4983,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="7">
         <v>1</v>
@@ -4995,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" s="7">
         <v>0</v>
@@ -5036,11 +4929,8 @@
       <c r="AG26" s="7">
         <v>0</v>
       </c>
-      <c r="AH26" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="27" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>0</v>
       </c>
@@ -5088,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="7">
         <v>1</v>
@@ -5097,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" s="7">
         <v>0</v>
@@ -5141,11 +5031,8 @@
       <c r="AG27" s="7">
         <v>0</v>
       </c>
-      <c r="AH27" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="28" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>0</v>
       </c>
@@ -5196,10 +5083,10 @@
         <v>0</v>
       </c>
       <c r="Q28" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" s="7">
         <v>0</v>
@@ -5246,11 +5133,8 @@
       <c r="AG28" s="7">
         <v>0</v>
       </c>
-      <c r="AH28" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="29" spans="1:34" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:33" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="15">
         <v>0</v>
       </c>
@@ -5345,17 +5229,14 @@
       <c r="AE29" s="16">
         <v>0</v>
       </c>
-      <c r="AF29" s="16">
+      <c r="AF29" s="7">
         <v>0</v>
       </c>
       <c r="AG29" s="7">
         <v>0</v>
       </c>
-      <c r="AH29" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="30" spans="1:34" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:33" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="15">
         <v>0</v>
       </c>
@@ -5450,17 +5331,14 @@
       <c r="AE30" s="16">
         <v>0</v>
       </c>
-      <c r="AF30" s="16">
+      <c r="AF30" s="7">
         <v>0</v>
       </c>
       <c r="AG30" s="7">
         <v>0</v>
       </c>
-      <c r="AH30" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="31" spans="1:34" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:33" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="15">
         <v>0</v>
       </c>
@@ -5555,17 +5433,14 @@
       <c r="AE31" s="16">
         <v>0</v>
       </c>
-      <c r="AF31" s="16">
+      <c r="AF31" s="7">
         <v>0</v>
       </c>
       <c r="AG31" s="7">
         <v>0</v>
       </c>
-      <c r="AH31" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="32" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>0</v>
       </c>
@@ -5619,10 +5494,10 @@
         <v>0</v>
       </c>
       <c r="R32" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" s="7">
         <v>0</v>
@@ -5666,11 +5541,8 @@
       <c r="AG32" s="7">
         <v>0</v>
       </c>
-      <c r="AH32" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="33" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>0</v>
       </c>
@@ -5724,10 +5596,10 @@
         <v>0</v>
       </c>
       <c r="R33" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" s="7">
         <v>0</v>
@@ -5771,11 +5643,8 @@
       <c r="AG33" s="7">
         <v>0</v>
       </c>
-      <c r="AH33" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="34" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>0</v>
       </c>
@@ -5829,13 +5698,13 @@
         <v>0</v>
       </c>
       <c r="R34" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" s="7">
         <v>1</v>
       </c>
       <c r="T34" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34" s="7">
         <v>0</v>
@@ -5876,11 +5745,8 @@
       <c r="AG34" s="7">
         <v>0</v>
       </c>
-      <c r="AH34" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="35" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>0</v>
       </c>
@@ -5934,10 +5800,10 @@
         <v>0</v>
       </c>
       <c r="R35" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" s="7">
         <v>0</v>
@@ -5981,11 +5847,8 @@
       <c r="AG35" s="7">
         <v>0</v>
       </c>
-      <c r="AH35" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="36" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>0</v>
       </c>
@@ -6039,13 +5902,13 @@
         <v>0</v>
       </c>
       <c r="R36" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" s="7">
         <v>1</v>
       </c>
       <c r="T36" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" s="7">
         <v>0</v>
@@ -6086,11 +5949,8 @@
       <c r="AG36" s="7">
         <v>0</v>
       </c>
-      <c r="AH36" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="37" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>0</v>
       </c>
@@ -6144,10 +6004,10 @@
         <v>0</v>
       </c>
       <c r="R37" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" s="7">
         <v>0</v>
@@ -6191,11 +6051,8 @@
       <c r="AG37" s="7">
         <v>0</v>
       </c>
-      <c r="AH37" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="38" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>0</v>
       </c>
@@ -6246,13 +6103,13 @@
         <v>0</v>
       </c>
       <c r="Q38" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="7">
         <v>1</v>
       </c>
       <c r="S38" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" s="7">
         <v>0</v>
@@ -6296,11 +6153,8 @@
       <c r="AG38" s="7">
         <v>0</v>
       </c>
-      <c r="AH38" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="39" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>0</v>
       </c>
@@ -6348,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="7">
         <v>1</v>
@@ -6357,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="S39" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" s="7">
         <v>0</v>
@@ -6401,11 +6255,8 @@
       <c r="AG39" s="7">
         <v>0</v>
       </c>
-      <c r="AH39" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="40" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>0</v>
       </c>
@@ -6456,13 +6307,13 @@
         <v>0</v>
       </c>
       <c r="Q40" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="7">
         <v>1</v>
       </c>
       <c r="S40" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" s="7">
         <v>0</v>
@@ -6506,11 +6357,8 @@
       <c r="AG40" s="7">
         <v>0</v>
       </c>
-      <c r="AH40" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="41" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>0</v>
       </c>
@@ -6558,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="7">
         <v>1</v>
@@ -6567,7 +6415,7 @@
         <v>1</v>
       </c>
       <c r="S41" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" s="7">
         <v>0</v>
@@ -6611,11 +6459,8 @@
       <c r="AG41" s="7">
         <v>0</v>
       </c>
-      <c r="AH41" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="42" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>0</v>
       </c>
@@ -6666,13 +6511,13 @@
         <v>0</v>
       </c>
       <c r="Q42" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="7">
         <v>1</v>
       </c>
       <c r="S42" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T42" s="7">
         <v>0</v>
@@ -6716,11 +6561,8 @@
       <c r="AG42" s="7">
         <v>0</v>
       </c>
-      <c r="AH42" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="43" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>0</v>
       </c>
@@ -6768,13 +6610,13 @@
         <v>1</v>
       </c>
       <c r="P43" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="7">
         <v>1</v>
       </c>
       <c r="R43" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" s="7">
         <v>0</v>
@@ -6821,11 +6663,8 @@
       <c r="AG43" s="7">
         <v>0</v>
       </c>
-      <c r="AH43" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="44" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>0</v>
       </c>
@@ -6876,10 +6715,10 @@
         <v>0</v>
       </c>
       <c r="Q44" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" s="7">
         <v>0</v>
@@ -6926,11 +6765,8 @@
       <c r="AG44" s="7">
         <v>0</v>
       </c>
-      <c r="AH44" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="45" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>0</v>
       </c>
@@ -6978,10 +6814,10 @@
         <v>0</v>
       </c>
       <c r="P45" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" s="7">
         <v>0</v>
@@ -7008,10 +6844,10 @@
         <v>0</v>
       </c>
       <c r="Z45" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA45" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="7">
         <v>0</v>
@@ -7031,11 +6867,8 @@
       <c r="AG45" s="7">
         <v>0</v>
       </c>
-      <c r="AH45" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="46" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>0</v>
       </c>
@@ -7083,13 +6916,13 @@
         <v>0</v>
       </c>
       <c r="P46" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="7">
         <v>1</v>
       </c>
       <c r="R46" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" s="7">
         <v>0</v>
@@ -7107,13 +6940,13 @@
         <v>0</v>
       </c>
       <c r="X46" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46" s="7">
         <v>1</v>
       </c>
       <c r="Z46" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="7">
         <v>0</v>
@@ -7136,11 +6969,8 @@
       <c r="AG46" s="7">
         <v>0</v>
       </c>
-      <c r="AH46" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="47" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>0</v>
       </c>
@@ -7197,13 +7027,13 @@
         <v>0</v>
       </c>
       <c r="S47" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="7">
         <v>1</v>
       </c>
       <c r="U47" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="7">
         <v>0</v>
@@ -7218,10 +7048,10 @@
         <v>0</v>
       </c>
       <c r="Z47" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA47" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" s="7">
         <v>0</v>
@@ -7241,11 +7071,8 @@
       <c r="AG47" s="7">
         <v>0</v>
       </c>
-      <c r="AH47" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="48" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>0</v>
       </c>
@@ -7323,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="Z48" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA48" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB48" s="7">
         <v>0</v>
@@ -7346,11 +7173,8 @@
       <c r="AG48" s="7">
         <v>0</v>
       </c>
-      <c r="AH48" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="49" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>0</v>
       </c>
@@ -7401,16 +7225,16 @@
         <v>0</v>
       </c>
       <c r="Q49" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49" s="7">
         <v>0</v>
@@ -7425,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="Y49" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="7">
         <v>0</v>
@@ -7451,11 +7275,8 @@
       <c r="AG49" s="7">
         <v>0</v>
       </c>
-      <c r="AH49" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="50" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>0</v>
       </c>
@@ -7506,10 +7327,10 @@
         <v>0</v>
       </c>
       <c r="Q50" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="7">
         <v>0</v>
@@ -7530,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="Y50" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z50" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA50" s="7">
         <v>0</v>
@@ -7556,11 +7377,8 @@
       <c r="AG50" s="7">
         <v>0</v>
       </c>
-      <c r="AH50" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="51" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>0</v>
       </c>
@@ -7608,10 +7426,10 @@
         <v>0</v>
       </c>
       <c r="P51" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" s="7">
         <v>0</v>
@@ -7638,10 +7456,10 @@
         <v>0</v>
       </c>
       <c r="Z51" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA51" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB51" s="7">
         <v>0</v>
@@ -7661,11 +7479,8 @@
       <c r="AG51" s="7">
         <v>0</v>
       </c>
-      <c r="AH51" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="52" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>0</v>
       </c>
@@ -7713,13 +7528,13 @@
         <v>0</v>
       </c>
       <c r="P52" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" s="7">
         <v>1</v>
       </c>
       <c r="R52" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" s="7">
         <v>0</v>
@@ -7737,13 +7552,13 @@
         <v>0</v>
       </c>
       <c r="X52" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" s="7">
         <v>1</v>
       </c>
       <c r="Z52" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="7">
         <v>0</v>
@@ -7766,11 +7581,8 @@
       <c r="AG52" s="7">
         <v>0</v>
       </c>
-      <c r="AH52" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="53" spans="1:34" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:33" s="19" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="15">
         <v>0</v>
       </c>
@@ -7865,17 +7677,14 @@
       <c r="AE53" s="16">
         <v>0</v>
       </c>
-      <c r="AF53" s="16">
+      <c r="AF53" s="7">
         <v>0</v>
       </c>
       <c r="AG53" s="7">
         <v>0</v>
       </c>
-      <c r="AH53" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="54" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>0</v>
       </c>
@@ -7932,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="S54" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U54" s="7">
         <v>0</v>
@@ -7944,10 +7753,10 @@
         <v>0</v>
       </c>
       <c r="W54" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="7">
         <v>0</v>
@@ -7976,11 +7785,8 @@
       <c r="AG54" s="7">
         <v>0</v>
       </c>
-      <c r="AH54" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="55" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>0</v>
       </c>
@@ -8037,19 +7843,19 @@
         <v>0</v>
       </c>
       <c r="S55" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U55" s="7">
         <v>0</v>
       </c>
       <c r="V55" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X55" s="7">
         <v>0</v>
@@ -8081,11 +7887,8 @@
       <c r="AG55" s="7">
         <v>0</v>
       </c>
-      <c r="AH55" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="56" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>0</v>
       </c>
@@ -8142,22 +7945,22 @@
         <v>0</v>
       </c>
       <c r="S56" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U56" s="7">
         <v>0</v>
       </c>
       <c r="V56" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="7">
         <v>1</v>
       </c>
       <c r="X56" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="7">
         <v>0</v>
@@ -8186,11 +7989,8 @@
       <c r="AG56" s="7">
         <v>0</v>
       </c>
-      <c r="AH56" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="57" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>0</v>
       </c>
@@ -8247,22 +8047,22 @@
         <v>0</v>
       </c>
       <c r="S57" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U57" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W57" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y57" s="7">
         <v>0</v>
@@ -8291,11 +8091,8 @@
       <c r="AG57" s="7">
         <v>0</v>
       </c>
-      <c r="AH57" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="58" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>0</v>
       </c>
@@ -8352,19 +8149,19 @@
         <v>0</v>
       </c>
       <c r="S58" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U58" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="7">
         <v>1</v>
       </c>
       <c r="W58" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X58" s="7">
         <v>0</v>
@@ -8396,11 +8193,8 @@
       <c r="AG58" s="7">
         <v>0</v>
       </c>
-      <c r="AH58" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="59" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>0</v>
       </c>
@@ -8457,13 +8251,13 @@
         <v>0</v>
       </c>
       <c r="S59" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U59" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" s="7">
         <v>1</v>
@@ -8472,7 +8266,7 @@
         <v>1</v>
       </c>
       <c r="X59" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="7">
         <v>0</v>
@@ -8501,11 +8295,8 @@
       <c r="AG59" s="7">
         <v>0</v>
       </c>
-      <c r="AH59" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="60" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>0</v>
       </c>
@@ -8556,16 +8347,16 @@
         <v>0</v>
       </c>
       <c r="Q60" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U60" s="7">
         <v>0</v>
@@ -8586,19 +8377,19 @@
         <v>0</v>
       </c>
       <c r="AA60" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB60" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC60" s="7">
         <v>0</v>
       </c>
       <c r="AD60" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE60" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF60" s="7">
         <v>0</v>
@@ -8606,11 +8397,8 @@
       <c r="AG60" s="7">
         <v>0</v>
       </c>
-      <c r="AH60" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="61" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>0</v>
       </c>
@@ -8691,10 +8479,10 @@
         <v>0</v>
       </c>
       <c r="AA61" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB61" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC61" s="7">
         <v>0</v>
@@ -8711,11 +8499,8 @@
       <c r="AG61" s="7">
         <v>0</v>
       </c>
-      <c r="AH61" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="62" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>0</v>
       </c>
@@ -8772,10 +8557,10 @@
         <v>0</v>
       </c>
       <c r="S62" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U62" s="7">
         <v>0</v>
@@ -8796,10 +8581,10 @@
         <v>0</v>
       </c>
       <c r="AA62" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB62" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC62" s="7">
         <v>0</v>
@@ -8816,11 +8601,8 @@
       <c r="AG62" s="7">
         <v>0</v>
       </c>
-      <c r="AH62" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="63" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>0</v>
       </c>
@@ -8883,10 +8665,10 @@
         <v>0</v>
       </c>
       <c r="U63" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V63" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W63" s="7">
         <v>0</v>
@@ -8921,11 +8703,8 @@
       <c r="AG63" s="7">
         <v>0</v>
       </c>
-      <c r="AH63" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="64" spans="1:34" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:33" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>0</v>
       </c>
@@ -8982,13 +8761,13 @@
         <v>0</v>
       </c>
       <c r="S64" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" s="7">
         <v>1</v>
       </c>
       <c r="U64" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V64" s="7">
         <v>0</v>
@@ -9009,10 +8788,10 @@
         <v>0</v>
       </c>
       <c r="AB64" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC64" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD64" s="7">
         <v>0</v>
@@ -9026,11 +8805,8 @@
       <c r="AG64" s="7">
         <v>0</v>
       </c>
-      <c r="AH64" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="65" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:45" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>0</v>
       </c>
@@ -9114,10 +8890,10 @@
         <v>0</v>
       </c>
       <c r="AB65" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC65" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD65" s="7">
         <v>0</v>
@@ -9131,11 +8907,8 @@
       <c r="AG65" s="7">
         <v>0</v>
       </c>
-      <c r="AH65" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="66" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:45" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>1</v>
       </c>
@@ -9183,10 +8956,10 @@
         <v>0</v>
       </c>
       <c r="P66" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" s="7">
         <v>0</v>
@@ -9219,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="AB66" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC66" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD66" s="7">
         <v>0</v>
@@ -9236,11 +9009,8 @@
       <c r="AG66" s="7">
         <v>0</v>
       </c>
-      <c r="AH66" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="67" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:45" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>1</v>
       </c>
@@ -9291,16 +9061,16 @@
         <v>0</v>
       </c>
       <c r="Q67" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U67" s="7">
         <v>0</v>
@@ -9312,10 +9082,10 @@
         <v>0</v>
       </c>
       <c r="X67" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y67" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z67" s="7">
         <v>0</v>
@@ -9327,10 +9097,10 @@
         <v>0</v>
       </c>
       <c r="AC67" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD67" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE67" s="7">
         <v>0</v>
@@ -9341,11 +9111,8 @@
       <c r="AG67" s="7">
         <v>0</v>
       </c>
-      <c r="AH67" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="68" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:45" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>1</v>
       </c>
@@ -9396,10 +9163,10 @@
         <v>0</v>
       </c>
       <c r="Q68" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" s="7">
         <v>0</v>
@@ -9417,10 +9184,10 @@
         <v>0</v>
       </c>
       <c r="X68" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y68" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z68" s="7">
         <v>0</v>
@@ -9432,10 +9199,10 @@
         <v>0</v>
       </c>
       <c r="AC68" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD68" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE68" s="7">
         <v>0</v>
@@ -9446,11 +9213,8 @@
       <c r="AG68" s="7">
         <v>0</v>
       </c>
-      <c r="AH68" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="69" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:45" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>1</v>
       </c>
@@ -9498,13 +9262,13 @@
         <v>0</v>
       </c>
       <c r="P69" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="7">
         <v>1</v>
       </c>
       <c r="R69" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69" s="7">
         <v>0</v>
@@ -9522,10 +9286,10 @@
         <v>0</v>
       </c>
       <c r="X69" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y69" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z69" s="7">
         <v>0</v>
@@ -9537,10 +9301,10 @@
         <v>0</v>
       </c>
       <c r="AC69" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD69" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE69" s="7">
         <v>0</v>
@@ -9551,11 +9315,8 @@
       <c r="AG69" s="7">
         <v>0</v>
       </c>
-      <c r="AH69" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="70" spans="1:46" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:45" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="9">
         <v>1</v>
       </c>
@@ -9636,10 +9397,10 @@
         <v>0</v>
       </c>
       <c r="AA70" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB70" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="7">
         <v>0</v>
@@ -9648,19 +9409,16 @@
         <v>0</v>
       </c>
       <c r="AE70" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF70" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG70" s="7">
         <v>0</v>
       </c>
-      <c r="AH70" s="7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="71" spans="1:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:45" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9">
         <v>1</v>
       </c>
@@ -9708,13 +9466,13 @@
         <v>0</v>
       </c>
       <c r="P71" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="7">
         <v>1</v>
       </c>
       <c r="R71" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" s="7">
         <v>0</v>
@@ -9732,10 +9490,10 @@
         <v>0</v>
       </c>
       <c r="X71" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z71" s="7">
         <v>0</v>
@@ -9756,14 +9514,12 @@
         <v>0</v>
       </c>
       <c r="AF71" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG71" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH71" s="7">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH71" s="5"/>
       <c r="AI71" s="5"/>
       <c r="AJ71" s="5"/>
       <c r="AK71" s="5"/>
@@ -9775,9 +9531,8 @@
       <c r="AQ71" s="5"/>
       <c r="AR71" s="5"/>
       <c r="AS71" s="5"/>
-      <c r="AT71" s="5"/>
     </row>
-    <row r="72" spans="1:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:45" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9">
         <v>1</v>
       </c>
@@ -9828,16 +9583,16 @@
         <v>0</v>
       </c>
       <c r="Q72" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U72" s="7">
         <v>0</v>
@@ -9873,14 +9628,12 @@
         <v>0</v>
       </c>
       <c r="AF72" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG72" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH72" s="7">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH72" s="5"/>
       <c r="AI72" s="5"/>
       <c r="AJ72" s="5"/>
       <c r="AK72" s="5"/>
@@ -9892,9 +9645,8 @@
       <c r="AQ72" s="5"/>
       <c r="AR72" s="5"/>
       <c r="AS72" s="5"/>
-      <c r="AT72" s="5"/>
     </row>
-    <row r="73" spans="1:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:45" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9">
         <v>1</v>
       </c>
@@ -9945,10 +9697,10 @@
         <v>0</v>
       </c>
       <c r="Q73" s="26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" s="26">
         <v>0</v>
@@ -9989,15 +9741,13 @@
       <c r="AE73" s="26">
         <v>0</v>
       </c>
-      <c r="AF73" s="26">
-        <v>0</v>
+      <c r="AF73" s="7">
+        <v>1</v>
       </c>
       <c r="AG73" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH73" s="7">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH73" s="5"/>
       <c r="AI73" s="5"/>
       <c r="AJ73" s="5"/>
       <c r="AK73" s="5"/>
@@ -10009,9 +9759,8 @@
       <c r="AQ73" s="5"/>
       <c r="AR73" s="5"/>
       <c r="AS73" s="5"/>
-      <c r="AT73" s="5"/>
     </row>
-    <row r="74" spans="1:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:45" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
         <v>1</v>
       </c>
@@ -10059,13 +9808,13 @@
         <v>0</v>
       </c>
       <c r="P74" s="26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" s="26">
         <v>1</v>
       </c>
       <c r="R74" s="26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" s="26">
         <v>0</v>
@@ -10083,10 +9832,10 @@
         <v>0</v>
       </c>
       <c r="X74" s="26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y74" s="26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z74" s="26">
         <v>0</v>
@@ -10106,15 +9855,13 @@
       <c r="AE74" s="26">
         <v>0</v>
       </c>
-      <c r="AF74" s="26">
-        <v>0</v>
+      <c r="AF74" s="7">
+        <v>1</v>
       </c>
       <c r="AG74" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH74" s="7">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH74" s="5"/>
       <c r="AI74" s="5"/>
       <c r="AJ74" s="5"/>
       <c r="AK74" s="5"/>
@@ -10126,9 +9873,8 @@
       <c r="AQ74" s="5"/>
       <c r="AR74" s="5"/>
       <c r="AS74" s="5"/>
-      <c r="AT74" s="5"/>
     </row>
-    <row r="75" spans="1:46" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:45" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="9">
         <v>1</v>
       </c>
@@ -10227,11 +9973,9 @@
         <v>0</v>
       </c>
       <c r="AG75" s="26">
-        <v>0</v>
-      </c>
-      <c r="AH75" s="26">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AH75" s="5"/>
       <c r="AI75" s="5"/>
       <c r="AJ75" s="5"/>
       <c r="AK75" s="5"/>
@@ -10243,26 +9987,13 @@
       <c r="AQ75" s="5"/>
       <c r="AR75" s="5"/>
       <c r="AS75" s="5"/>
-      <c r="AT75" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="H34:H35">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:AH75">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color theme="0"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I74:AF75 AG75:AH75">
+  <conditionalFormatting sqref="AF75:AG75 I74:AE75">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10274,8 +10005,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I72:AG72 I73:AF73 AG73:AG75 AH75">
+  <conditionalFormatting sqref="AF73:AF75 I72:AF72 I73:AE73 AG75">
     <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:AG75">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10451,20 +10194,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="58f9fe6c-3eae-457f-9e87-44d8d431dd39" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="58f9fe6c-3eae-457f-9e87-44d8d431dd39" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10486,6 +10229,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CBAD53F-4BA0-4A62-B9AA-EF58C4C7C2BE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EB6F3A0-5884-4EF3-BA6D-772E0A3CD2DB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -10499,12 +10250,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CBAD53F-4BA0-4A62-B9AA-EF58C4C7C2BE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>